--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98748</v>
+        <v>98750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98750</v>
+        <v>98837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98837</v>
+        <v>98840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98840</v>
+        <v>98866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98866</v>
+        <v>98867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98867</v>
+        <v>98868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 8429-2025 artfynd.xlsx
+++ b/artfynd/A 8429-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130191550</v>
       </c>
       <c r="B2" t="n">
-        <v>98870</v>
+        <v>98874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
